--- a/data/trans_camb/IP43-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP43-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 0,43</t>
+          <t>-17,84; -0,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,06; -13,2</t>
+          <t>-26,95; -12,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,89; -0,4</t>
+          <t>-18,24; -0,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,24; -15,75</t>
+          <t>-31,52; -16,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,12; -3,24</t>
+          <t>-15,24; -2,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,68; -16,89</t>
+          <t>-26,46; -17,0</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 8,76</t>
+          <t>-71,23; 0,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,89; 3,08</t>
+          <t>-64,24; 2,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,16; -16,94</t>
+          <t>-61,73; -15,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,11; -4,63</t>
+          <t>-21,69; -5,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,31; -12,76</t>
+          <t>-27,18; -13,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -4,52</t>
+          <t>-19,64; -4,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,41; -13,62</t>
+          <t>-27,4; -14,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,68; -6,53</t>
+          <t>-17,82; -6,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -15,22</t>
+          <t>-24,33; -15,43</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,2; -30,37</t>
+          <t>-84,1; -34,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,97; -27,19</t>
+          <t>-79,2; -30,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,49; -39,23</t>
+          <t>-75,47; -40,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,25; -2,95</t>
+          <t>-24,17; -4,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,08; -18,99</t>
+          <t>-35,1; -19,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,7; -0,17</t>
+          <t>-21,05; 0,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,57; -18,99</t>
+          <t>-35,08; -18,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,55; -3,44</t>
+          <t>-18,52; -5,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,44; -21,07</t>
+          <t>-31,97; -21,25</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,52; -11,06</t>
+          <t>-76,25; -19,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 0,9</t>
+          <t>-66,31; 2,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,01; -15,34</t>
+          <t>-62,98; -21,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 0,14</t>
+          <t>-12,0; -0,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,05; -16,92</t>
+          <t>-26,34; -17,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,61; -5,65</t>
+          <t>-17,54; -5,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-28,75; -18,94</t>
+          <t>-28,14; -18,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,61; -3,67</t>
+          <t>-13,2; -4,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,75; -19,24</t>
+          <t>-25,97; -19,15</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 0,15</t>
+          <t>-49,6; -1,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,42; -25,43</t>
+          <t>-64,38; -26,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,33; -19,48</t>
+          <t>-52,92; -22,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -3,5</t>
+          <t>-19,85; -3,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-36,15; -23,92</t>
+          <t>-36,26; -24,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,18; -7,11</t>
+          <t>-22,38; -6,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-34,17; -21,5</t>
+          <t>-33,95; -21,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,25; -7,45</t>
+          <t>-18,81; -7,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,82; -24,66</t>
+          <t>-33,38; -24,44</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,11; -13,62</t>
+          <t>-57,71; -14,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,24; -30,77</t>
+          <t>-69,72; -23,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-58,24; -28,51</t>
+          <t>-59,54; -29,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-17,35; -1,5</t>
+          <t>-17,63; -1,82</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,37; -6,0</t>
+          <t>-21,53; -6,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,64</t>
+          <t>-8,74; 5,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -4,48</t>
+          <t>-15,94; -4,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 0,31</t>
+          <t>-10,54; 1,22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,03; -6,69</t>
+          <t>-15,46; -6,63</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-94,21; -4,44</t>
+          <t>-93,63; -3,07</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-69,75; 147,18</t>
+          <t>-70,59; 133,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-77,09; 8,14</t>
+          <t>-75,83; 22,8</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-13,28; -6,97</t>
+          <t>-13,32; -6,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-25,62; -20,34</t>
+          <t>-25,24; -20,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,8; -7,33</t>
+          <t>-14,01; -7,59</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-25,08; -20,01</t>
+          <t>-25,17; -20,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -7,63</t>
+          <t>-12,74; -8,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -20,86</t>
+          <t>-24,42; -20,79</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,29; -32,84</t>
+          <t>-54,08; -31,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,46; -35,78</t>
+          <t>-57,78; -36,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-52,44; -35,85</t>
+          <t>-53,0; -37,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
